--- a/output/yearly_total_coral_cover_iteration_43_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_43_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.285811103487214</v>
+        <v>1.277220811075054</v>
       </c>
       <c r="C3" t="n">
-        <v>4.609371139595121</v>
+        <v>4.580605931860689</v>
       </c>
       <c r="D3" t="n">
-        <v>6.058046108837827</v>
+        <v>6.064879072859385</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95322835192016</v>
+        <v>11.92270581579513</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.463202487870555</v>
+        <v>1.440077761144385</v>
       </c>
       <c r="C4" t="n">
-        <v>5.086121712213044</v>
+        <v>4.982211563796422</v>
       </c>
       <c r="D4" t="n">
-        <v>6.304455831642725</v>
+        <v>6.442215287053918</v>
       </c>
       <c r="E4" t="n">
-        <v>12.85378003172632</v>
+        <v>12.86450461199473</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.703703299531564</v>
+        <v>1.673646158742292</v>
       </c>
       <c r="C5" t="n">
-        <v>5.675729982768286</v>
+        <v>5.49438408214705</v>
       </c>
       <c r="D5" t="n">
-        <v>6.675759950965297</v>
+        <v>6.807658591644491</v>
       </c>
       <c r="E5" t="n">
-        <v>14.05519323326515</v>
+        <v>13.97568883253383</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.969171379325275</v>
+        <v>1.944971599379295</v>
       </c>
       <c r="C6" t="n">
-        <v>6.360737611116278</v>
+        <v>6.140613940244057</v>
       </c>
       <c r="D6" t="n">
-        <v>7.063363394434979</v>
+        <v>7.18054349153649</v>
       </c>
       <c r="E6" t="n">
-        <v>15.39327238487653</v>
+        <v>15.26612903115984</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.266687940057919</v>
+        <v>2.243104386174466</v>
       </c>
       <c r="C7" t="n">
-        <v>7.135210227596813</v>
+        <v>6.931579135565729</v>
       </c>
       <c r="D7" t="n">
-        <v>7.488067698160545</v>
+        <v>7.5869270408322</v>
       </c>
       <c r="E7" t="n">
-        <v>16.88996586581528</v>
+        <v>16.76161056257239</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.448398016913776</v>
+        <v>1.443929559830775</v>
       </c>
       <c r="C8" t="n">
-        <v>4.685658186940299</v>
+        <v>4.738237528997573</v>
       </c>
       <c r="D8" t="n">
-        <v>5.752902939646925</v>
+        <v>5.946147323845644</v>
       </c>
       <c r="E8" t="n">
-        <v>11.886959143501</v>
+        <v>12.12831441267399</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.844753315797533</v>
+        <v>1.836022317463252</v>
       </c>
       <c r="C9" t="n">
-        <v>5.617651751868986</v>
+        <v>5.874780591671691</v>
       </c>
       <c r="D9" t="n">
-        <v>6.406110156327753</v>
+        <v>6.530522998630805</v>
       </c>
       <c r="E9" t="n">
-        <v>13.86851522399427</v>
+        <v>14.24132590776575</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.259222060732459</v>
+        <v>2.261719637946066</v>
       </c>
       <c r="C10" t="n">
-        <v>6.6732609749974</v>
+        <v>7.185578616875018</v>
       </c>
       <c r="D10" t="n">
-        <v>7.006091898763857</v>
+        <v>7.19747585600099</v>
       </c>
       <c r="E10" t="n">
-        <v>15.93857493449372</v>
+        <v>16.64477411082207</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.681214116068684</v>
+        <v>2.672755995783822</v>
       </c>
       <c r="C11" t="n">
-        <v>7.85076768913007</v>
+        <v>8.602446004151462</v>
       </c>
       <c r="D11" t="n">
-        <v>7.697454010917761</v>
+        <v>7.888701401240792</v>
       </c>
       <c r="E11" t="n">
-        <v>18.22943581611651</v>
+        <v>19.16390340117607</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.102407035961185</v>
+        <v>3.095789267706092</v>
       </c>
       <c r="C12" t="n">
-        <v>9.107374428753442</v>
+        <v>10.10583176177409</v>
       </c>
       <c r="D12" t="n">
-        <v>8.459755889491431</v>
+        <v>8.509932747585516</v>
       </c>
       <c r="E12" t="n">
-        <v>20.66953735420606</v>
+        <v>21.7115537770657</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.510381860196886</v>
+        <v>3.491049468426782</v>
       </c>
       <c r="C13" t="n">
-        <v>10.41598241516946</v>
+        <v>11.63766464796205</v>
       </c>
       <c r="D13" t="n">
-        <v>9.072271140704514</v>
+        <v>9.088106198955582</v>
       </c>
       <c r="E13" t="n">
-        <v>22.99863541607086</v>
+        <v>24.21682031534441</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.025777482851039</v>
+        <v>2.003501627441678</v>
       </c>
       <c r="C14" t="n">
-        <v>7.412391516604267</v>
+        <v>8.085222488232777</v>
       </c>
       <c r="D14" t="n">
-        <v>6.94250743039766</v>
+        <v>6.914822145137899</v>
       </c>
       <c r="E14" t="n">
-        <v>16.38067642985297</v>
+        <v>17.00354626081235</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.081530934975215</v>
+        <v>2.064311080242726</v>
       </c>
       <c r="C15" t="n">
-        <v>7.919238403875769</v>
+        <v>8.818489848534719</v>
       </c>
       <c r="D15" t="n">
-        <v>7.097545027852316</v>
+        <v>7.018612512430873</v>
       </c>
       <c r="E15" t="n">
-        <v>17.0983143667033</v>
+        <v>17.90141344120832</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.431985412960199</v>
+        <v>2.403936881049868</v>
       </c>
       <c r="C16" t="n">
-        <v>9.316000315138833</v>
+        <v>10.51750242550425</v>
       </c>
       <c r="D16" t="n">
-        <v>7.725264692470683</v>
+        <v>7.644879190446956</v>
       </c>
       <c r="E16" t="n">
-        <v>19.47325042056972</v>
+        <v>20.56631849700107</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.954276797550744</v>
+        <v>1.929301135954705</v>
       </c>
       <c r="C17" t="n">
-        <v>8.58308638401042</v>
+        <v>9.844092222730234</v>
       </c>
       <c r="D17" t="n">
-        <v>7.269213431416913</v>
+        <v>7.17950132620284</v>
       </c>
       <c r="E17" t="n">
-        <v>17.80657661297808</v>
+        <v>18.95289468488778</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.238325860820473</v>
+        <v>2.20152013938826</v>
       </c>
       <c r="C18" t="n">
-        <v>9.977109219178635</v>
+        <v>11.55322661853055</v>
       </c>
       <c r="D18" t="n">
-        <v>7.853186418334043</v>
+        <v>7.712855401489003</v>
       </c>
       <c r="E18" t="n">
-        <v>20.06862149833315</v>
+        <v>21.46760215940781</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.258549863527958</v>
+        <v>2.205044613646506</v>
       </c>
       <c r="C19" t="n">
-        <v>10.64716184480412</v>
+        <v>12.42808163273897</v>
       </c>
       <c r="D19" t="n">
-        <v>8.066824536255192</v>
+        <v>7.872153783980092</v>
       </c>
       <c r="E19" t="n">
-        <v>20.97253624458727</v>
+        <v>22.50528003036557</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.53871120588887</v>
+        <v>2.459042379689241</v>
       </c>
       <c r="C20" t="n">
-        <v>12.20799343240092</v>
+        <v>14.275622819884</v>
       </c>
       <c r="D20" t="n">
-        <v>8.664060934656696</v>
+        <v>8.408600364534633</v>
       </c>
       <c r="E20" t="n">
-        <v>23.41076557294648</v>
+        <v>25.14326556410787</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.524536374970787</v>
+        <v>1.464846114552581</v>
       </c>
       <c r="C21" t="n">
-        <v>8.989078329624647</v>
+        <v>10.48659700777456</v>
       </c>
       <c r="D21" t="n">
-        <v>7.316435495991185</v>
+        <v>7.065657862418379</v>
       </c>
       <c r="E21" t="n">
-        <v>17.83005020058662</v>
+        <v>19.01710098474552</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_43_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_43_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.277220811075054</v>
+        <v>1.26376105004983</v>
       </c>
       <c r="C3" t="n">
-        <v>4.580605931860689</v>
+        <v>4.58725236381844</v>
       </c>
       <c r="D3" t="n">
-        <v>6.064879072859385</v>
+        <v>6.065625201114613</v>
       </c>
       <c r="E3" t="n">
-        <v>11.92270581579513</v>
+        <v>11.91663861498288</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.440077761144385</v>
+        <v>1.402291336251758</v>
       </c>
       <c r="C4" t="n">
-        <v>4.982211563796422</v>
+        <v>5.001979612006504</v>
       </c>
       <c r="D4" t="n">
-        <v>6.442215287053918</v>
+        <v>6.349567879056362</v>
       </c>
       <c r="E4" t="n">
-        <v>12.86450461199473</v>
+        <v>12.75383882731462</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.673646158742292</v>
+        <v>1.590298450675853</v>
       </c>
       <c r="C5" t="n">
-        <v>5.49438408214705</v>
+        <v>5.521801117782442</v>
       </c>
       <c r="D5" t="n">
-        <v>6.807658591644491</v>
+        <v>6.66657632527312</v>
       </c>
       <c r="E5" t="n">
-        <v>13.97568883253383</v>
+        <v>13.77867589373141</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.944971599379295</v>
+        <v>1.804134196078417</v>
       </c>
       <c r="C6" t="n">
-        <v>6.140613940244057</v>
+        <v>6.138966188493274</v>
       </c>
       <c r="D6" t="n">
-        <v>7.18054349153649</v>
+        <v>7.022442114454284</v>
       </c>
       <c r="E6" t="n">
-        <v>15.26612903115984</v>
+        <v>14.96554249902598</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.243104386174466</v>
+        <v>2.041925916746201</v>
       </c>
       <c r="C7" t="n">
-        <v>6.931579135565729</v>
+        <v>6.865788820491514</v>
       </c>
       <c r="D7" t="n">
-        <v>7.5869270408322</v>
+        <v>7.469068245295984</v>
       </c>
       <c r="E7" t="n">
-        <v>16.76161056257239</v>
+        <v>16.3767829825337</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.443929559830775</v>
+        <v>1.252381471385992</v>
       </c>
       <c r="C8" t="n">
-        <v>4.738237528997573</v>
+        <v>4.474104351335018</v>
       </c>
       <c r="D8" t="n">
-        <v>5.946147323845644</v>
+        <v>5.754422344281395</v>
       </c>
       <c r="E8" t="n">
-        <v>12.12831441267399</v>
+        <v>11.48090816700241</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.836022317463252</v>
+        <v>1.577551148284627</v>
       </c>
       <c r="C9" t="n">
-        <v>5.874780591671691</v>
+        <v>5.331437897999344</v>
       </c>
       <c r="D9" t="n">
-        <v>6.530522998630805</v>
+        <v>6.32000242089742</v>
       </c>
       <c r="E9" t="n">
-        <v>14.24132590776575</v>
+        <v>13.22899146718139</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.261719637946066</v>
+        <v>1.929443846829109</v>
       </c>
       <c r="C10" t="n">
-        <v>7.185578616875018</v>
+        <v>6.28273479071504</v>
       </c>
       <c r="D10" t="n">
-        <v>7.19747585600099</v>
+        <v>6.854116133303087</v>
       </c>
       <c r="E10" t="n">
-        <v>16.64477411082207</v>
+        <v>15.06629477084724</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.672755995783822</v>
+        <v>2.303908210700348</v>
       </c>
       <c r="C11" t="n">
-        <v>8.602446004151462</v>
+        <v>7.309936731687332</v>
       </c>
       <c r="D11" t="n">
-        <v>7.888701401240792</v>
+        <v>7.426613935740994</v>
       </c>
       <c r="E11" t="n">
-        <v>19.16390340117607</v>
+        <v>17.04045887812867</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.095789267706092</v>
+        <v>2.687207739163739</v>
       </c>
       <c r="C12" t="n">
-        <v>10.10583176177409</v>
+        <v>8.429250686383517</v>
       </c>
       <c r="D12" t="n">
-        <v>8.509932747585516</v>
+        <v>7.994221012939263</v>
       </c>
       <c r="E12" t="n">
-        <v>21.7115537770657</v>
+        <v>19.11067943848652</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.491049468426782</v>
+        <v>3.079011039084481</v>
       </c>
       <c r="C13" t="n">
-        <v>11.63766464796205</v>
+        <v>9.630547698857285</v>
       </c>
       <c r="D13" t="n">
-        <v>9.088106198955582</v>
+        <v>8.526523456362668</v>
       </c>
       <c r="E13" t="n">
-        <v>24.21682031534441</v>
+        <v>21.23608219430443</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.003501627441678</v>
+        <v>1.785308200172825</v>
       </c>
       <c r="C14" t="n">
-        <v>8.085222488232777</v>
+        <v>6.903748031033996</v>
       </c>
       <c r="D14" t="n">
-        <v>6.914822145137899</v>
+        <v>6.492660814834728</v>
       </c>
       <c r="E14" t="n">
-        <v>17.00354626081235</v>
+        <v>15.18171704604155</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.064311080242726</v>
+        <v>1.852459743143307</v>
       </c>
       <c r="C15" t="n">
-        <v>8.818489848534719</v>
+        <v>7.317976839886851</v>
       </c>
       <c r="D15" t="n">
-        <v>7.018612512430873</v>
+        <v>6.555620295108076</v>
       </c>
       <c r="E15" t="n">
-        <v>17.90141344120832</v>
+        <v>15.72605687813823</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.403936881049868</v>
+        <v>2.179794062693278</v>
       </c>
       <c r="C16" t="n">
-        <v>10.51750242550425</v>
+        <v>8.596447970265219</v>
       </c>
       <c r="D16" t="n">
-        <v>7.644879190446956</v>
+        <v>7.105978240631796</v>
       </c>
       <c r="E16" t="n">
-        <v>20.56631849700107</v>
+        <v>17.88222027359029</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.929301135954705</v>
+        <v>1.762747637929233</v>
       </c>
       <c r="C17" t="n">
-        <v>9.844092222730234</v>
+        <v>7.943644651803345</v>
       </c>
       <c r="D17" t="n">
-        <v>7.17950132620284</v>
+        <v>6.638656515933272</v>
       </c>
       <c r="E17" t="n">
-        <v>18.95289468488778</v>
+        <v>16.34504880566585</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.20152013938826</v>
+        <v>2.049584864679024</v>
       </c>
       <c r="C18" t="n">
-        <v>11.55322661853055</v>
+        <v>9.223539316352868</v>
       </c>
       <c r="D18" t="n">
-        <v>7.712855401489003</v>
+        <v>7.169782023930797</v>
       </c>
       <c r="E18" t="n">
-        <v>21.46760215940781</v>
+        <v>18.44290620496269</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.205044613646506</v>
+        <v>2.096316055401172</v>
       </c>
       <c r="C19" t="n">
-        <v>12.42808163273897</v>
+        <v>9.847950491207923</v>
       </c>
       <c r="D19" t="n">
-        <v>7.872153783980092</v>
+        <v>7.350364696649955</v>
       </c>
       <c r="E19" t="n">
-        <v>22.50528003036557</v>
+        <v>19.29463124325905</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.459042379689241</v>
+        <v>2.380973802247535</v>
       </c>
       <c r="C20" t="n">
-        <v>14.275622819884</v>
+        <v>11.33290279874348</v>
       </c>
       <c r="D20" t="n">
-        <v>8.408600364534633</v>
+        <v>7.863975825603715</v>
       </c>
       <c r="E20" t="n">
-        <v>25.14326556410787</v>
+        <v>21.57785242659473</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.464846114552581</v>
+        <v>1.445171890559475</v>
       </c>
       <c r="C21" t="n">
-        <v>10.48659700777456</v>
+        <v>8.392401527414563</v>
       </c>
       <c r="D21" t="n">
-        <v>7.065657862418379</v>
+        <v>6.582422007434015</v>
       </c>
       <c r="E21" t="n">
-        <v>19.01710098474552</v>
+        <v>16.41999542540805</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_43_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_43_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.26376105004983</v>
+        <v>2.590802260959735</v>
       </c>
       <c r="C3" t="n">
-        <v>4.58725236381844</v>
+        <v>7.692952544880427</v>
       </c>
       <c r="D3" t="n">
-        <v>6.065625201114613</v>
+        <v>8.153844457817049</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91663861498288</v>
+        <v>18.43759926365721</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.402291336251758</v>
+        <v>1.073439843128084</v>
       </c>
       <c r="C4" t="n">
-        <v>5.001979612006504</v>
+        <v>4.436660367751346</v>
       </c>
       <c r="D4" t="n">
-        <v>6.349567879056362</v>
+        <v>5.748928472057626</v>
       </c>
       <c r="E4" t="n">
-        <v>12.75383882731462</v>
+        <v>11.25902868293706</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.590298450675853</v>
+        <v>1.171143383911726</v>
       </c>
       <c r="C5" t="n">
-        <v>5.521801117782442</v>
+        <v>4.978979143451799</v>
       </c>
       <c r="D5" t="n">
-        <v>6.66657632527312</v>
+        <v>6.088931723200071</v>
       </c>
       <c r="E5" t="n">
-        <v>13.77867589373141</v>
+        <v>12.2390542505636</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.804134196078417</v>
+        <v>1.277077440002902</v>
       </c>
       <c r="C6" t="n">
-        <v>6.138966188493274</v>
+        <v>5.621861632516512</v>
       </c>
       <c r="D6" t="n">
-        <v>7.022442114454284</v>
+        <v>6.498327200561834</v>
       </c>
       <c r="E6" t="n">
-        <v>14.96554249902598</v>
+        <v>13.39726627308125</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.041925916746201</v>
+        <v>1.39702489459215</v>
       </c>
       <c r="C7" t="n">
-        <v>6.865788820491514</v>
+        <v>6.370417451260603</v>
       </c>
       <c r="D7" t="n">
-        <v>7.469068245295984</v>
+        <v>6.896562748271903</v>
       </c>
       <c r="E7" t="n">
-        <v>16.3767829825337</v>
+        <v>14.66400509412466</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.252381471385992</v>
+        <v>1.516364046691722</v>
       </c>
       <c r="C8" t="n">
-        <v>4.474104351335018</v>
+        <v>7.20879239356725</v>
       </c>
       <c r="D8" t="n">
-        <v>5.754422344281395</v>
+        <v>7.344492798533626</v>
       </c>
       <c r="E8" t="n">
-        <v>11.48090816700241</v>
+        <v>16.0696492387926</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.577551148284627</v>
+        <v>1.64946480072576</v>
       </c>
       <c r="C9" t="n">
-        <v>5.331437897999344</v>
+        <v>8.202913570131095</v>
       </c>
       <c r="D9" t="n">
-        <v>6.32000242089742</v>
+        <v>7.891429993301636</v>
       </c>
       <c r="E9" t="n">
-        <v>13.22899146718139</v>
+        <v>17.74380836415849</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.929443846829109</v>
+        <v>1.037717140865921</v>
       </c>
       <c r="C10" t="n">
-        <v>6.28273479071504</v>
+        <v>6.212096955915075</v>
       </c>
       <c r="D10" t="n">
-        <v>6.854116133303087</v>
+        <v>6.255264402470806</v>
       </c>
       <c r="E10" t="n">
-        <v>15.06629477084724</v>
+        <v>13.5050784992518</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.303908210700348</v>
+        <v>0.9789006359044946</v>
       </c>
       <c r="C11" t="n">
-        <v>7.309936731687332</v>
+        <v>6.465731475307239</v>
       </c>
       <c r="D11" t="n">
-        <v>7.426613935740994</v>
+        <v>6.204802570472521</v>
       </c>
       <c r="E11" t="n">
-        <v>17.04045887812867</v>
+        <v>13.64943468168425</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.687207739163739</v>
+        <v>1.067680080799534</v>
       </c>
       <c r="C12" t="n">
-        <v>8.429250686383517</v>
+        <v>7.604735526820303</v>
       </c>
       <c r="D12" t="n">
-        <v>7.994221012939263</v>
+        <v>6.72286101652652</v>
       </c>
       <c r="E12" t="n">
-        <v>19.11067943848652</v>
+        <v>15.39527662414636</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.079011039084481</v>
+        <v>0.8524809840286329</v>
       </c>
       <c r="C13" t="n">
-        <v>9.630547698857285</v>
+        <v>7.253721452643898</v>
       </c>
       <c r="D13" t="n">
-        <v>8.526523456362668</v>
+        <v>6.231614100275501</v>
       </c>
       <c r="E13" t="n">
-        <v>21.23608219430443</v>
+        <v>14.33781653694803</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.785308200172825</v>
+        <v>0.9333573599044852</v>
       </c>
       <c r="C14" t="n">
-        <v>6.903748031033996</v>
+        <v>8.525644325834939</v>
       </c>
       <c r="D14" t="n">
-        <v>6.492660814834728</v>
+        <v>6.705189557850079</v>
       </c>
       <c r="E14" t="n">
-        <v>15.18171704604155</v>
+        <v>16.1641912435895</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.852459743143307</v>
+        <v>0.9140856524701203</v>
       </c>
       <c r="C15" t="n">
-        <v>7.317976839886851</v>
+        <v>9.243508064657249</v>
       </c>
       <c r="D15" t="n">
-        <v>6.555620295108076</v>
+        <v>6.84446028717453</v>
       </c>
       <c r="E15" t="n">
-        <v>15.72605687813823</v>
+        <v>17.0020540043019</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.179794062693278</v>
+        <v>1.013193083213836</v>
       </c>
       <c r="C16" t="n">
-        <v>8.596447970265219</v>
+        <v>10.87454443058473</v>
       </c>
       <c r="D16" t="n">
-        <v>7.105978240631796</v>
+        <v>7.352446001782958</v>
       </c>
       <c r="E16" t="n">
-        <v>17.88222027359029</v>
+        <v>19.24018351558152</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.762747637929233</v>
+        <v>0.6172051467058848</v>
       </c>
       <c r="C17" t="n">
-        <v>7.943644651803345</v>
+        <v>8.294707813364962</v>
       </c>
       <c r="D17" t="n">
-        <v>6.638656515933272</v>
+        <v>6.171128624216855</v>
       </c>
       <c r="E17" t="n">
-        <v>16.34504880566585</v>
+        <v>15.0830415842877</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.049584864679024</v>
+        <v>0.4938583651443155</v>
       </c>
       <c r="C18" t="n">
-        <v>9.223539316352868</v>
+        <v>7.423161288919855</v>
       </c>
       <c r="D18" t="n">
-        <v>7.169782023930797</v>
+        <v>5.698741081364417</v>
       </c>
       <c r="E18" t="n">
-        <v>18.44290620496269</v>
+        <v>13.61576073542859</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.096316055401172</v>
+        <v>0.5846602103101031</v>
       </c>
       <c r="C19" t="n">
-        <v>9.847950491207923</v>
+        <v>9.238010277513467</v>
       </c>
       <c r="D19" t="n">
-        <v>7.350364696649955</v>
+        <v>6.253860503253735</v>
       </c>
       <c r="E19" t="n">
-        <v>19.29463124325905</v>
+        <v>16.07653099107731</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.380973802247535</v>
+        <v>0.6693261323243479</v>
       </c>
       <c r="C20" t="n">
-        <v>11.33290279874348</v>
+        <v>11.23962694936299</v>
       </c>
       <c r="D20" t="n">
-        <v>7.863975825603715</v>
+        <v>6.852922952385137</v>
       </c>
       <c r="E20" t="n">
-        <v>21.57785242659473</v>
+        <v>18.76187603407248</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.445171890559475</v>
+        <v>0.7495152848072274</v>
       </c>
       <c r="C21" t="n">
-        <v>8.392401527414563</v>
+        <v>13.27663562595061</v>
       </c>
       <c r="D21" t="n">
-        <v>6.582422007434015</v>
+        <v>7.355823213885567</v>
       </c>
       <c r="E21" t="n">
-        <v>16.41999542540805</v>
+        <v>21.38197412464341</v>
       </c>
     </row>
   </sheetData>
